--- a/Measurements_Fie.xlsx
+++ b/Measurements_Fie.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fionn\OneDrive\Documents\tudelft\MSc\Q4\Fieldwork\B_Module_Fieldwork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D161A4-015B-4821-AB37-986BD4781896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517715CF-77A8-4938-BBCD-7494888D1B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample_overview" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="58">
   <si>
     <t>Location</t>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>delta_h+</t>
+  </si>
+  <si>
+    <t>pH_field</t>
   </si>
 </sst>
 </file>
@@ -1396,14 +1399,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B8BD1F-4FFD-4618-B27E-AB3915771674}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>52</v>
       </c>
@@ -1419,8 +1422,11 @@
       <c r="F1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -1446,8 +1452,11 @@
         <f>AVERAGE(F2:F4)</f>
         <v>-4.6457768336846478E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <v>0.90700000000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -1470,7 +1479,7 @@
         <v>-4.6084729822224904E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -1493,7 +1502,7 @@
         <v>-4.3262538079022306E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -1520,7 +1529,7 @@
         <v>-4.2222071112735314E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -1543,7 +1552,7 @@
         <v>-3.967051151848161E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>48</v>
       </c>
@@ -1566,7 +1575,7 @@
         <v>-4.3497850909862169E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -1593,7 +1602,7 @@
         <v>-4.9284267797321486E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -1616,7 +1625,7 @@
         <v>-3.8865282300790199E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -1637,6 +1646,12 @@
       <c r="F10">
         <f t="shared" si="2"/>
         <v>-3.5343881133840099E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <f>AVERAGE(B2:B10)</f>
+        <v>1.3144444444444445</v>
       </c>
     </row>
   </sheetData>
@@ -1646,10 +1661,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3588D47-CB0D-4CC7-889D-D3172F5695C6}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>52</v>
       </c>
@@ -1665,8 +1680,11 @@
       <c r="F1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -1692,8 +1710,11 @@
         <f>AVERAGE(F2:F4)</f>
         <v>-3.4839460362788462E-3</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <v>2.2890000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -1717,7 +1738,7 @@
       </c>
       <c r="G3" s="50"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -1741,7 +1762,7 @@
       </c>
       <c r="G4" s="50"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -1768,7 +1789,7 @@
         <v>-3.4434057134730828E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -1792,7 +1813,7 @@
       </c>
       <c r="G6" s="50"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>48</v>
       </c>
@@ -1816,7 +1837,7 @@
       </c>
       <c r="G7" s="50"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -1843,7 +1864,7 @@
         <v>-4.2483622364676609E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -1867,7 +1888,7 @@
       </c>
       <c r="G9" s="50"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -1890,6 +1911,12 @@
         <v>-3.9794498954376124E-3</v>
       </c>
       <c r="G10" s="50"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <f>AVERAGE(B2:B10)</f>
+        <v>2.4333333333333327</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1898,10 +1925,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2008C058-829C-4317-9A39-BD204D2E9EE3}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>52</v>
       </c>
@@ -1917,8 +1944,11 @@
       <c r="F1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -1940,9 +1970,15 @@
         <f t="shared" ref="F2:F10" si="2">E2-D2</f>
         <v>-5.7536407957965354E-3</v>
       </c>
-      <c r="G2" s="50"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G2" s="50">
+        <f>AVERAGE(F2:F4)</f>
+        <v>-5.4157973145259981E-3</v>
+      </c>
+      <c r="H2">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -1966,7 +2002,7 @@
       </c>
       <c r="G3" s="50"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -1988,36 +2024,35 @@
         <f t="shared" si="2"/>
         <v>-5.2464527924003645E-3</v>
       </c>
-      <c r="G4" s="50">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="C5">
+        <v>6.08</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>4.7863009232263836E-3</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>8.3176377110266907E-7</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="2"/>
+        <v>-4.7854691594552811E-3</v>
+      </c>
+      <c r="G5" s="50">
         <f>AVERAGE(F4:F6)</f>
         <v>-5.092370840950081E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5">
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="C5">
-        <v>6.08</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>4.7863009232263836E-3</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="1"/>
-        <v>8.3176377110266907E-7</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="2"/>
-        <v>-4.7854691594552811E-3</v>
-      </c>
-      <c r="G5" s="50"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -2041,7 +2076,7 @@
       </c>
       <c r="G6" s="50"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>48</v>
       </c>
@@ -2063,36 +2098,35 @@
         <f t="shared" si="2"/>
         <v>-5.2345849736718068E-3</v>
       </c>
-      <c r="G7" s="50">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="C8">
+        <v>5.58</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>4.7863009232263836E-3</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>2.630267991895377E-6</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="2"/>
+        <v>-4.7836706552344885E-3</v>
+      </c>
+      <c r="G8" s="50">
         <f>AVERAGE(F7:F9)</f>
         <v>-5.0875940325038945E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8">
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="C8">
-        <v>5.58</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>4.7863009232263836E-3</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="1"/>
-        <v>2.630267991895377E-6</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="2"/>
-        <v>-4.7836706552344885E-3</v>
-      </c>
-      <c r="G8" s="50"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -2114,9 +2148,8 @@
         <f t="shared" si="2"/>
         <v>-5.2445264686053882E-3</v>
       </c>
-      <c r="G9" s="50"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -2139,6 +2172,12 @@
         <v>-5.2417650290529222E-3</v>
       </c>
       <c r="G10" s="50"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <f>AVERAGE(B2:B10)</f>
+        <v>2.2844444444444445</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2147,10 +2186,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48990189-1E96-46A1-B6CC-1AC605A7B280}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>52</v>
       </c>
@@ -2166,8 +2205,11 @@
       <c r="F1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -2193,8 +2235,11 @@
         <f>AVERAGE(F2:F4)</f>
         <v>-2.3105099419454978E-3</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -2218,7 +2263,7 @@
       </c>
       <c r="G3" s="50"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -2242,7 +2287,7 @@
       </c>
       <c r="G4" s="50"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -2269,7 +2314,7 @@
         <v>-2.3278306423024833E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -2293,7 +2338,7 @@
       </c>
       <c r="G6" s="50"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>48</v>
       </c>
@@ -2317,7 +2362,7 @@
       </c>
       <c r="G7" s="50"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -2344,7 +2389,7 @@
         <v>-2.3103596834068716E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -2368,7 +2413,7 @@
       </c>
       <c r="G9" s="50"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -2391,6 +2436,12 @@
         <v>-2.2382534034270513E-3</v>
       </c>
       <c r="G10" s="50"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <f>AVERAGE(B2:B10)</f>
+        <v>2.6355555555555554</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
